--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_25.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:M151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,4535 +469,6780 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:54.804</t>
+          <t>2026-05-29 09:46:18.301</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779509210066</v>
+        <v>1780022775611</v>
       </c>
       <c r="C2" t="n">
-        <v>86899</v>
+        <v>75033</v>
       </c>
       <c r="D2" t="n">
-        <v>-150.68</v>
+        <v>-799.02</v>
       </c>
       <c r="E2" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F2" t="n">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="G2" t="n">
-        <v>74.55</v>
+        <v>330.46</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J2" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2689</v>
+      </c>
+      <c r="L2" t="n">
+        <v>110</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.141</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:54.805</t>
+          <t>2026-05-29 09:46:18.304</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779509210267</v>
+        <v>1780022775811</v>
       </c>
       <c r="C3" t="n">
-        <v>86950</v>
+        <v>75129</v>
       </c>
       <c r="D3" t="n">
-        <v>-92.15000000000001</v>
+        <v>-663.0700000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F3" t="n">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="G3" t="n">
-        <v>74.55</v>
+        <v>330.46</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J3" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2491</v>
+      </c>
+      <c r="L3" t="n">
+        <v>117</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.451</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:54.807</t>
+          <t>2026-05-29 09:46:18.543</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779509210469</v>
+        <v>1780022777330</v>
       </c>
       <c r="C4" t="n">
-        <v>86994</v>
+        <v>74936</v>
       </c>
       <c r="D4" t="n">
-        <v>-43.54</v>
+        <v>-822.91</v>
       </c>
       <c r="E4" t="n">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="F4" t="n">
-        <v>664</v>
+        <v>1359</v>
       </c>
       <c r="G4" t="n">
-        <v>68.73999999999999</v>
+        <v>363.36</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>99.27</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1212</v>
+      </c>
+      <c r="L4" t="n">
+        <v>106</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.572</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:55.140</t>
+          <t>2026-05-29 09:46:18.544</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779509210670</v>
+        <v>1780022777530</v>
       </c>
       <c r="C5" t="n">
-        <v>86845</v>
+        <v>74819</v>
       </c>
       <c r="D5" t="n">
-        <v>-190.37</v>
+        <v>-898.77</v>
       </c>
       <c r="E5" t="n">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="F5" t="n">
-        <v>664</v>
+        <v>1359</v>
       </c>
       <c r="G5" t="n">
-        <v>68.73999999999999</v>
+        <v>363.36</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1013</v>
+      </c>
+      <c r="L5" t="n">
+        <v>116</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:55.385</t>
+          <t>2026-05-29 09:46:18.848</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779509210871</v>
+        <v>1780022777731</v>
       </c>
       <c r="C6" t="n">
-        <v>87045</v>
+        <v>74728</v>
       </c>
       <c r="D6" t="n">
-        <v>19.15</v>
+        <v>-944.83</v>
       </c>
       <c r="E6" t="n">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="F6" t="n">
-        <v>664</v>
+        <v>1359</v>
       </c>
       <c r="G6" t="n">
-        <v>68.73999999999999</v>
+        <v>363.36</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.63</v>
+      </c>
+      <c r="J6" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1115</v>
+      </c>
+      <c r="L6" t="n">
+        <v>166</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.538</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:55.393</t>
+          <t>2026-05-29 09:46:18.850</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779509211072</v>
+        <v>1780022777930</v>
       </c>
       <c r="C7" t="n">
-        <v>87343</v>
+        <v>74724</v>
       </c>
       <c r="D7" t="n">
-        <v>316.19</v>
+        <v>-901.59</v>
       </c>
       <c r="E7" t="n">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="F7" t="n">
-        <v>564</v>
+        <v>1359</v>
       </c>
       <c r="G7" t="n">
-        <v>65.95</v>
+        <v>363.36</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K7" t="n">
+        <v>919</v>
+      </c>
+      <c r="L7" t="n">
+        <v>146</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.695</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:55.394</t>
+          <t>2026-05-29 09:46:18.851</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779509211274</v>
+        <v>1780022778130</v>
       </c>
       <c r="C8" t="n">
-        <v>87633</v>
+        <v>74642</v>
       </c>
       <c r="D8" t="n">
-        <v>590.38</v>
+        <v>-938.51</v>
       </c>
       <c r="E8" t="n">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="F8" t="n">
-        <v>564</v>
+        <v>1359</v>
       </c>
       <c r="G8" t="n">
-        <v>65.95</v>
+        <v>363.36</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K8" t="n">
+        <v>720</v>
+      </c>
+      <c r="L8" t="n">
+        <v>134</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.878</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:55.656</t>
+          <t>2026-05-29 09:46:19.274</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779509211475</v>
+        <v>1780022778330</v>
       </c>
       <c r="C9" t="n">
-        <v>87270</v>
+        <v>74585</v>
       </c>
       <c r="D9" t="n">
-        <v>197.87</v>
+        <v>-948.58</v>
       </c>
       <c r="E9" t="n">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="F9" t="n">
-        <v>564</v>
+        <v>1359</v>
       </c>
       <c r="G9" t="n">
-        <v>65.95</v>
+        <v>363.36</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K9" t="n">
+        <v>943</v>
+      </c>
+      <c r="L9" t="n">
+        <v>121</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.435</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:55.664</t>
+          <t>2026-05-29 09:46:19.320</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779509211676</v>
+        <v>1780022778530</v>
       </c>
       <c r="C10" t="n">
-        <v>87673</v>
+        <v>74464</v>
       </c>
       <c r="D10" t="n">
-        <v>590.97</v>
+        <v>-1022.15</v>
       </c>
       <c r="E10" t="n">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="F10" t="n">
-        <v>564</v>
+        <v>1359</v>
       </c>
       <c r="G10" t="n">
-        <v>65.95</v>
+        <v>363.36</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K10" t="n">
+        <v>789</v>
+      </c>
+      <c r="L10" t="n">
+        <v>110</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.031</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:56.441</t>
+          <t>2026-05-29 09:46:19.651</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779509211878</v>
+        <v>1780022778749</v>
       </c>
       <c r="C11" t="n">
-        <v>87019</v>
+        <v>74396</v>
       </c>
       <c r="D11" t="n">
-        <v>-92.58</v>
+        <v>-1039.05</v>
       </c>
       <c r="E11" t="n">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="F11" t="n">
-        <v>564</v>
+        <v>1359</v>
       </c>
       <c r="G11" t="n">
-        <v>65.95</v>
+        <v>363.36</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K11" t="n">
+        <v>901</v>
+      </c>
+      <c r="L11" t="n">
+        <v>121</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.591</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:56.720</t>
+          <t>2026-05-29 09:46:19.660</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779509212079</v>
+        <v>1780022778949</v>
       </c>
       <c r="C12" t="n">
-        <v>87293</v>
+        <v>74267</v>
       </c>
       <c r="D12" t="n">
-        <v>186.05</v>
+        <v>-1116.09</v>
       </c>
       <c r="E12" t="n">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="F12" t="n">
-        <v>564</v>
+        <v>1359</v>
       </c>
       <c r="G12" t="n">
-        <v>65.95</v>
+        <v>363.36</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K12" t="n">
+        <v>709</v>
+      </c>
+      <c r="L12" t="n">
+        <v>101</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.619</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:56.723</t>
+          <t>2026-05-29 09:46:20.076</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779509212280</v>
+        <v>1780022779149</v>
       </c>
       <c r="C13" t="n">
-        <v>87444</v>
+        <v>74363</v>
       </c>
       <c r="D13" t="n">
-        <v>327.75</v>
+        <v>-964.29</v>
       </c>
       <c r="E13" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F13" t="n">
-        <v>1328</v>
+        <v>1359</v>
       </c>
       <c r="G13" t="n">
-        <v>223</v>
+        <v>363.36</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K13" t="n">
+        <v>926</v>
+      </c>
+      <c r="L13" t="n">
+        <v>116</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:56.724</t>
+          <t>2026-05-29 09:46:20.078</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779509212482</v>
+        <v>1780022779349</v>
       </c>
       <c r="C14" t="n">
-        <v>87208</v>
+        <v>74539</v>
       </c>
       <c r="D14" t="n">
-        <v>75.36</v>
+        <v>-740.08</v>
       </c>
       <c r="E14" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F14" t="n">
-        <v>1328</v>
+        <v>1359</v>
       </c>
       <c r="G14" t="n">
-        <v>223</v>
+        <v>363.36</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K14" t="n">
+        <v>728</v>
+      </c>
+      <c r="L14" t="n">
+        <v>108</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.005</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:56.996</t>
+          <t>2026-05-29 09:46:20.564</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779509212683</v>
+        <v>1780022779549</v>
       </c>
       <c r="C15" t="n">
-        <v>88764</v>
+        <v>74794</v>
       </c>
       <c r="D15" t="n">
-        <v>1627.59</v>
+        <v>-448.07</v>
       </c>
       <c r="E15" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F15" t="n">
-        <v>1328</v>
+        <v>3438</v>
       </c>
       <c r="G15" t="n">
-        <v>223</v>
+        <v>363.36</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1013</v>
+      </c>
+      <c r="L15" t="n">
+        <v>119</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.038</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:57.003</t>
+          <t>2026-05-29 09:46:20.573</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779509212884</v>
+        <v>1780022779749</v>
       </c>
       <c r="C16" t="n">
-        <v>88830</v>
+        <v>75148</v>
       </c>
       <c r="D16" t="n">
-        <v>1612.21</v>
+        <v>-71.67</v>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F16" t="n">
-        <v>1328</v>
+        <v>3438</v>
       </c>
       <c r="G16" t="n">
-        <v>223</v>
+        <v>363.36</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K16" t="n">
+        <v>823</v>
+      </c>
+      <c r="L16" t="n">
+        <v>110</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.253</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:57.040</t>
+          <t>2026-05-29 09:46:20.877</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779509213085</v>
+        <v>1780022779949</v>
       </c>
       <c r="C17" t="n">
-        <v>88340</v>
+        <v>75437</v>
       </c>
       <c r="D17" t="n">
-        <v>1041.6</v>
+        <v>220.92</v>
       </c>
       <c r="E17" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F17" t="n">
-        <v>1328</v>
+        <v>3438</v>
       </c>
       <c r="G17" t="n">
-        <v>223</v>
+        <v>363.36</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K17" t="n">
+        <v>927</v>
+      </c>
+      <c r="L17" t="n">
+        <v>110</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.123</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:57.486</t>
+          <t>2026-05-29 09:46:20.906</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779509213287</v>
+        <v>1780022780168</v>
       </c>
       <c r="C18" t="n">
-        <v>88581</v>
+        <v>75266</v>
       </c>
       <c r="D18" t="n">
-        <v>1230.52</v>
+        <v>38.87</v>
       </c>
       <c r="E18" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F18" t="n">
-        <v>1328</v>
+        <v>3438</v>
       </c>
       <c r="G18" t="n">
-        <v>223</v>
+        <v>363.36</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K18" t="n">
+        <v>737</v>
+      </c>
+      <c r="L18" t="n">
+        <v>109</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.238</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:57.754</t>
+          <t>2026-05-29 09:46:21.285</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779509213488</v>
+        <v>1780022780368</v>
       </c>
       <c r="C19" t="n">
-        <v>88854</v>
+        <v>75032</v>
       </c>
       <c r="D19" t="n">
-        <v>1442</v>
+        <v>-197.07</v>
       </c>
       <c r="E19" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F19" t="n">
-        <v>1328</v>
+        <v>3438</v>
       </c>
       <c r="G19" t="n">
-        <v>223</v>
+        <v>363.36</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I19" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K19" t="n">
+        <v>916</v>
+      </c>
+      <c r="L19" t="n">
+        <v>116</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.014</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:58.008</t>
+          <t>2026-05-29 09:46:21.286</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779509213689</v>
+        <v>1780022780568</v>
       </c>
       <c r="C20" t="n">
-        <v>88564</v>
+        <v>74996</v>
       </c>
       <c r="D20" t="n">
-        <v>1079.9</v>
+        <v>-223.22</v>
       </c>
       <c r="E20" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F20" t="n">
-        <v>1328</v>
+        <v>3438</v>
       </c>
       <c r="G20" t="n">
-        <v>223</v>
+        <v>363.36</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K20" t="n">
+        <v>717</v>
+      </c>
+      <c r="L20" t="n">
+        <v>109</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.8080000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:58.009</t>
+          <t>2026-05-29 09:46:21.811</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779509213891</v>
+        <v>1780022780768</v>
       </c>
       <c r="C21" t="n">
-        <v>88726</v>
+        <v>74863</v>
       </c>
       <c r="D21" t="n">
-        <v>1187.9</v>
+        <v>-345.06</v>
       </c>
       <c r="E21" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F21" t="n">
-        <v>1328</v>
+        <v>3438</v>
       </c>
       <c r="G21" t="n">
-        <v>223</v>
+        <v>363.36</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1042</v>
+      </c>
+      <c r="L21" t="n">
+        <v>122</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.572</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:58.010</t>
+          <t>2026-05-29 09:46:21.811</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1779509214092</v>
+        <v>1780022780968</v>
       </c>
       <c r="C22" t="n">
-        <v>88920</v>
+        <v>74651</v>
       </c>
       <c r="D22" t="n">
-        <v>1322.51</v>
+        <v>-539.8099999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F22" t="n">
-        <v>1328</v>
+        <v>3438</v>
       </c>
       <c r="G22" t="n">
-        <v>223</v>
+        <v>363.36</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K22" t="n">
+        <v>843</v>
+      </c>
+      <c r="L22" t="n">
+        <v>106</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.515</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:58.413</t>
+          <t>2026-05-29 09:46:22.151</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1779509214293</v>
+        <v>1780022781168</v>
       </c>
       <c r="C23" t="n">
-        <v>88451</v>
+        <v>74675</v>
       </c>
       <c r="D23" t="n">
-        <v>787.38</v>
+        <v>-488.82</v>
       </c>
       <c r="E23" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F23" t="n">
-        <v>1328</v>
+        <v>3438</v>
       </c>
       <c r="G23" t="n">
-        <v>223</v>
+        <v>363.36</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K23" t="n">
+        <v>982</v>
+      </c>
+      <c r="L23" t="n">
+        <v>112</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.966</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:58.643</t>
+          <t>2026-05-29 09:46:22.152</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1779509214495</v>
+        <v>1780022781368</v>
       </c>
       <c r="C24" t="n">
-        <v>88601</v>
+        <v>74844</v>
       </c>
       <c r="D24" t="n">
-        <v>898.01</v>
+        <v>-295.37</v>
       </c>
       <c r="E24" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F24" t="n">
-        <v>1328</v>
+        <v>3438</v>
       </c>
       <c r="G24" t="n">
-        <v>223</v>
+        <v>363.36</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K24" t="n">
+        <v>783</v>
+      </c>
+      <c r="L24" t="n">
+        <v>121</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.745</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:58.916</t>
+          <t>2026-05-29 09:46:22.655</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1779509214696</v>
+        <v>1780022781568</v>
       </c>
       <c r="C25" t="n">
-        <v>88327</v>
+        <v>74823</v>
       </c>
       <c r="D25" t="n">
-        <v>579.11</v>
+        <v>-301.61</v>
       </c>
       <c r="E25" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F25" t="n">
-        <v>1328</v>
+        <v>2139</v>
       </c>
       <c r="G25" t="n">
-        <v>223</v>
+        <v>363.36</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J25" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1086</v>
+      </c>
+      <c r="L25" t="n">
+        <v>118</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.259</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:58.917</t>
+          <t>2026-05-29 09:46:22.656</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1779509214897</v>
+        <v>1780022781768</v>
       </c>
       <c r="C26" t="n">
-        <v>88033</v>
+        <v>74916</v>
       </c>
       <c r="D26" t="n">
-        <v>256.16</v>
+        <v>-193.53</v>
       </c>
       <c r="E26" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F26" t="n">
-        <v>1328</v>
+        <v>2139</v>
       </c>
       <c r="G26" t="n">
-        <v>223</v>
+        <v>363.36</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K26" t="n">
+        <v>887</v>
+      </c>
+      <c r="L26" t="n">
+        <v>109</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.894</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:59.527</t>
+          <t>2026-05-29 09:46:22.941</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1779509215099</v>
+        <v>1780022781987</v>
       </c>
       <c r="C27" t="n">
-        <v>88030</v>
+        <v>75037</v>
       </c>
       <c r="D27" t="n">
-        <v>240.35</v>
+        <v>-62.85</v>
       </c>
       <c r="E27" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F27" t="n">
-        <v>1328</v>
+        <v>2139</v>
       </c>
       <c r="G27" t="n">
-        <v>223</v>
+        <v>363.36</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K27" t="n">
+        <v>953</v>
+      </c>
+      <c r="L27" t="n">
+        <v>119</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:59.775</t>
+          <t>2026-05-29 09:46:22.942</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1779509215300</v>
+        <v>1780022782187</v>
       </c>
       <c r="C28" t="n">
-        <v>88152</v>
+        <v>75210</v>
       </c>
       <c r="D28" t="n">
-        <v>350.33</v>
+        <v>113.29</v>
       </c>
       <c r="E28" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F28" t="n">
-        <v>1328</v>
+        <v>2139</v>
       </c>
       <c r="G28" t="n">
-        <v>223</v>
+        <v>363.36</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J28" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K28" t="n">
+        <v>754</v>
+      </c>
+      <c r="L28" t="n">
+        <v>106</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.877</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-23 11:06:59.798</t>
+          <t>2026-05-29 09:46:23.423</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1779509215501</v>
+        <v>1780022782387</v>
       </c>
       <c r="C29" t="n">
-        <v>88174</v>
+        <v>74982</v>
       </c>
       <c r="D29" t="n">
-        <v>354.81</v>
+        <v>-120.37</v>
       </c>
       <c r="E29" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F29" t="n">
-        <v>1328</v>
+        <v>2139</v>
       </c>
       <c r="G29" t="n">
-        <v>223</v>
+        <v>363.36</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J29" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1035</v>
+      </c>
+      <c r="L29" t="n">
+        <v>116</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.028</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:00.035</t>
+          <t>2026-05-29 09:46:23.425</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1779509215703</v>
+        <v>1780022782587</v>
       </c>
       <c r="C30" t="n">
-        <v>88066</v>
+        <v>75017</v>
       </c>
       <c r="D30" t="n">
-        <v>229.07</v>
+        <v>-79.34999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F30" t="n">
-        <v>3241</v>
+        <v>2139</v>
       </c>
       <c r="G30" t="n">
-        <v>223</v>
+        <v>363.36</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K30" t="n">
+        <v>837</v>
+      </c>
+      <c r="L30" t="n">
+        <v>109</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.959</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:00.037</t>
+          <t>2026-05-29 09:46:23.945</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1779509215904</v>
+        <v>1780022782787</v>
       </c>
       <c r="C31" t="n">
-        <v>88194</v>
+        <v>75194</v>
       </c>
       <c r="D31" t="n">
-        <v>345.62</v>
+        <v>101.61</v>
       </c>
       <c r="E31" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F31" t="n">
-        <v>3241</v>
+        <v>1139</v>
       </c>
       <c r="G31" t="n">
-        <v>223</v>
+        <v>370.08</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1157</v>
+      </c>
+      <c r="L31" t="n">
+        <v>122</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.113</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:00.039</t>
+          <t>2026-05-29 09:46:23.947</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1779509216105</v>
+        <v>1780022782987</v>
       </c>
       <c r="C32" t="n">
-        <v>88382</v>
+        <v>75320</v>
       </c>
       <c r="D32" t="n">
-        <v>516.34</v>
+        <v>222.53</v>
       </c>
       <c r="E32" t="n">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="F32" t="n">
-        <v>484</v>
+        <v>1139</v>
       </c>
       <c r="G32" t="n">
-        <v>234.05</v>
+        <v>370.08</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I32" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K32" t="n">
+        <v>959</v>
+      </c>
+      <c r="L32" t="n">
+        <v>109</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.449</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:00.565</t>
+          <t>2026-05-29 09:46:24.187</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1779509216307</v>
+        <v>1780022783187</v>
       </c>
       <c r="C33" t="n">
-        <v>87960</v>
+        <v>75241</v>
       </c>
       <c r="D33" t="n">
-        <v>68.52</v>
+        <v>132.41</v>
       </c>
       <c r="E33" t="n">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="F33" t="n">
-        <v>484</v>
+        <v>1139</v>
       </c>
       <c r="G33" t="n">
-        <v>234.05</v>
+        <v>370.08</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K33" t="n">
+        <v>998</v>
+      </c>
+      <c r="L33" t="n">
+        <v>116</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.631</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:00.801</t>
+          <t>2026-05-29 09:46:24.188</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1779509216508</v>
+        <v>1780022783387</v>
       </c>
       <c r="C34" t="n">
-        <v>88138</v>
+        <v>75538</v>
       </c>
       <c r="D34" t="n">
-        <v>243.1</v>
+        <v>422.79</v>
       </c>
       <c r="E34" t="n">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="F34" t="n">
-        <v>484</v>
+        <v>1139</v>
       </c>
       <c r="G34" t="n">
-        <v>234.05</v>
+        <v>370.08</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K34" t="n">
+        <v>800</v>
+      </c>
+      <c r="L34" t="n">
+        <v>109</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.014</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:00.814</t>
+          <t>2026-05-29 09:46:24.587</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1779509216709</v>
+        <v>1780022783606</v>
       </c>
       <c r="C35" t="n">
-        <v>88373</v>
+        <v>75876</v>
       </c>
       <c r="D35" t="n">
-        <v>465.94</v>
+        <v>739.65</v>
       </c>
       <c r="E35" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F35" t="n">
-        <v>684</v>
+        <v>1139</v>
       </c>
       <c r="G35" t="n">
-        <v>233.7</v>
+        <v>370.08</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K35" t="n">
+        <v>981</v>
+      </c>
+      <c r="L35" t="n">
+        <v>119</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.533</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:01.051</t>
+          <t>2026-05-29 09:46:24.595</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1779509216910</v>
+        <v>1780022783806</v>
       </c>
       <c r="C36" t="n">
-        <v>88167</v>
+        <v>75574</v>
       </c>
       <c r="D36" t="n">
-        <v>236.64</v>
+        <v>400.66</v>
       </c>
       <c r="E36" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F36" t="n">
-        <v>684</v>
+        <v>1139</v>
       </c>
       <c r="G36" t="n">
-        <v>233.7</v>
+        <v>370.08</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K36" t="n">
+        <v>788</v>
+      </c>
+      <c r="L36" t="n">
+        <v>109</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.471</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:01.322</t>
+          <t>2026-05-29 09:46:25.079</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1779509217112</v>
+        <v>1780022784006</v>
       </c>
       <c r="C37" t="n">
-        <v>88314</v>
+        <v>75498</v>
       </c>
       <c r="D37" t="n">
-        <v>371.81</v>
+        <v>304.63</v>
       </c>
       <c r="E37" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F37" t="n">
-        <v>684</v>
+        <v>1139</v>
       </c>
       <c r="G37" t="n">
-        <v>233.7</v>
+        <v>370.08</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I37" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1073</v>
+      </c>
+      <c r="L37" t="n">
+        <v>114</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.57</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:01.323</t>
+          <t>2026-05-29 09:46:25.081</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1779509217313</v>
+        <v>1780022784206</v>
       </c>
       <c r="C38" t="n">
-        <v>88442</v>
+        <v>75462</v>
       </c>
       <c r="D38" t="n">
-        <v>481.22</v>
+        <v>253.4</v>
       </c>
       <c r="E38" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F38" t="n">
-        <v>564</v>
+        <v>1139</v>
       </c>
       <c r="G38" t="n">
-        <v>236.59</v>
+        <v>370.08</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J38" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K38" t="n">
+        <v>874</v>
+      </c>
+      <c r="L38" t="n">
+        <v>107</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.402</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:01.692</t>
+          <t>2026-05-29 09:46:25.784</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1779509217514</v>
+        <v>1780022784406</v>
       </c>
       <c r="C39" t="n">
-        <v>88422</v>
+        <v>75230</v>
       </c>
       <c r="D39" t="n">
-        <v>437.16</v>
+        <v>8.73</v>
       </c>
       <c r="E39" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F39" t="n">
-        <v>564</v>
+        <v>1139</v>
       </c>
       <c r="G39" t="n">
-        <v>236.59</v>
+        <v>370.08</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1377</v>
+      </c>
+      <c r="L39" t="n">
+        <v>115</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.991</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:01.927</t>
+          <t>2026-05-29 09:46:25.785</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1779509217716</v>
+        <v>1780022784606</v>
       </c>
       <c r="C40" t="n">
-        <v>88041</v>
+        <v>75175</v>
       </c>
       <c r="D40" t="n">
-        <v>34.3</v>
+        <v>-46.71</v>
       </c>
       <c r="E40" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F40" t="n">
-        <v>564</v>
+        <v>1139</v>
       </c>
       <c r="G40" t="n">
-        <v>236.59</v>
+        <v>370.08</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1178</v>
+      </c>
+      <c r="L40" t="n">
+        <v>109</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.949</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:02.217</t>
+          <t>2026-05-29 09:46:26.191</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1779509217917</v>
+        <v>1780022784806</v>
       </c>
       <c r="C41" t="n">
-        <v>88187</v>
+        <v>75182</v>
       </c>
       <c r="D41" t="n">
-        <v>178.59</v>
+        <v>-37.37</v>
       </c>
       <c r="E41" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F41" t="n">
-        <v>564</v>
+        <v>1139</v>
       </c>
       <c r="G41" t="n">
-        <v>236.59</v>
+        <v>370.08</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1384</v>
+      </c>
+      <c r="L41" t="n">
+        <v>114</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.311</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:02.218</t>
+          <t>2026-05-29 09:46:26.198</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1779509218118</v>
+        <v>1780022785006</v>
       </c>
       <c r="C42" t="n">
-        <v>88141</v>
+        <v>75214</v>
       </c>
       <c r="D42" t="n">
-        <v>123.66</v>
+        <v>-3.5</v>
       </c>
       <c r="E42" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F42" t="n">
-        <v>564</v>
+        <v>1139</v>
       </c>
       <c r="G42" t="n">
-        <v>236.59</v>
+        <v>370.08</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1191</v>
+      </c>
+      <c r="L42" t="n">
+        <v>111</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:02.219</t>
+          <t>2026-05-29 09:46:26.224</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1779509218320</v>
+        <v>1780022785225</v>
       </c>
       <c r="C43" t="n">
-        <v>87988</v>
+        <v>74990</v>
       </c>
       <c r="D43" t="n">
-        <v>-35.52</v>
+        <v>-227.33</v>
       </c>
       <c r="E43" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F43" t="n">
-        <v>564</v>
+        <v>1139</v>
       </c>
       <c r="G43" t="n">
-        <v>236.59</v>
+        <v>370.08</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J43" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K43" t="n">
+        <v>999</v>
+      </c>
+      <c r="L43" t="n">
+        <v>120</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.627</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:02.595</t>
+          <t>2026-05-29 09:46:27.083</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1779509218521</v>
+        <v>1780022785426</v>
       </c>
       <c r="C44" t="n">
-        <v>87873</v>
+        <v>75006</v>
       </c>
       <c r="D44" t="n">
-        <v>-148.75</v>
+        <v>-199.96</v>
       </c>
       <c r="E44" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F44" t="n">
-        <v>564</v>
+        <v>1139</v>
       </c>
       <c r="G44" t="n">
-        <v>236.59</v>
+        <v>370.08</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I44" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="J44" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1656</v>
+      </c>
+      <c r="L44" t="n">
+        <v>106</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.988</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:02.937</t>
+          <t>2026-05-29 09:46:27.110</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1779509218722</v>
+        <v>1780022785625</v>
       </c>
       <c r="C45" t="n">
-        <v>88306</v>
+        <v>75122</v>
       </c>
       <c r="D45" t="n">
-        <v>291.69</v>
+        <v>-73.95999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F45" t="n">
-        <v>564</v>
+        <v>1139</v>
       </c>
       <c r="G45" t="n">
-        <v>236.59</v>
+        <v>370.08</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J45" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1484</v>
+      </c>
+      <c r="L45" t="n">
+        <v>114</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.724</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:03.140</t>
+          <t>2026-05-29 09:46:27.543</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1779509218924</v>
+        <v>1780022785825</v>
       </c>
       <c r="C46" t="n">
-        <v>88098</v>
+        <v>75066</v>
       </c>
       <c r="D46" t="n">
-        <v>69.09999999999999</v>
+        <v>-126.26</v>
       </c>
       <c r="E46" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F46" t="n">
-        <v>1570</v>
+        <v>3138</v>
       </c>
       <c r="G46" t="n">
-        <v>236.59</v>
+        <v>370.08</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I46" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1717</v>
+      </c>
+      <c r="L46" t="n">
+        <v>115</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.865</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:03.147</t>
+          <t>2026-05-29 09:46:27.544</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1779509219125</v>
+        <v>1780022786025</v>
       </c>
       <c r="C47" t="n">
-        <v>87899</v>
+        <v>75816</v>
       </c>
       <c r="D47" t="n">
-        <v>-133.35</v>
+        <v>630.05</v>
       </c>
       <c r="E47" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F47" t="n">
-        <v>1570</v>
+        <v>200</v>
       </c>
       <c r="G47" t="n">
-        <v>236.59</v>
+        <v>370.08</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I47" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J47" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1518</v>
+      </c>
+      <c r="L47" t="n">
+        <v>104</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.533</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:03.518</t>
+          <t>2026-05-29 09:46:27.551</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1779509219326</v>
+        <v>1780022786225</v>
       </c>
       <c r="C48" t="n">
-        <v>88127</v>
+        <v>74922</v>
       </c>
       <c r="D48" t="n">
-        <v>101.32</v>
+        <v>-295.45</v>
       </c>
       <c r="E48" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F48" t="n">
-        <v>1570</v>
+        <v>200</v>
       </c>
       <c r="G48" t="n">
-        <v>236.59</v>
+        <v>370.08</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J48" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L48" t="n">
+        <v>106</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.625</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:03.793</t>
+          <t>2026-05-29 09:46:27.588</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1779509219528</v>
+        <v>1780022786425</v>
       </c>
       <c r="C49" t="n">
-        <v>88733</v>
+        <v>74431</v>
       </c>
       <c r="D49" t="n">
-        <v>702.25</v>
+        <v>-771.6799999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="F49" t="n">
-        <v>624</v>
+        <v>200</v>
       </c>
       <c r="G49" t="n">
-        <v>235.18</v>
+        <v>370.08</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I49" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J49" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1162</v>
+      </c>
+      <c r="L49" t="n">
+        <v>105</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.5570000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:04.147</t>
+          <t>2026-05-29 09:46:28.456</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1779509219729</v>
+        <v>1780022786644</v>
       </c>
       <c r="C50" t="n">
-        <v>87875</v>
+        <v>74348</v>
       </c>
       <c r="D50" t="n">
-        <v>-190.86</v>
+        <v>-816.1</v>
       </c>
       <c r="E50" t="n">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="F50" t="n">
-        <v>624</v>
+        <v>200</v>
       </c>
       <c r="G50" t="n">
-        <v>235.18</v>
+        <v>370.08</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I50" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1811</v>
+      </c>
+      <c r="L50" t="n">
+        <v>111</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.024</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:04.407</t>
+          <t>2026-05-29 09:46:28.457</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1779509219930</v>
+        <v>1780022786844</v>
       </c>
       <c r="C51" t="n">
-        <v>88160</v>
+        <v>74905</v>
       </c>
       <c r="D51" t="n">
-        <v>103.68</v>
+        <v>-218.29</v>
       </c>
       <c r="E51" t="n">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="F51" t="n">
-        <v>624</v>
+        <v>200</v>
       </c>
       <c r="G51" t="n">
-        <v>235.18</v>
+        <v>370.08</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J51" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1612</v>
+      </c>
+      <c r="L51" t="n">
+        <v>105</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.982</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:04.408</t>
+          <t>2026-05-29 09:46:28.492</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1779509220132</v>
+        <v>1780022787044</v>
       </c>
       <c r="C52" t="n">
-        <v>88343</v>
+        <v>74873</v>
       </c>
       <c r="D52" t="n">
-        <v>281.5</v>
+        <v>-239.38</v>
       </c>
       <c r="E52" t="n">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="F52" t="n">
-        <v>624</v>
+        <v>200</v>
       </c>
       <c r="G52" t="n">
-        <v>235.18</v>
+        <v>370.08</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I52" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J52" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1447</v>
+      </c>
+      <c r="L52" t="n">
+        <v>105</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.032</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:04.693</t>
+          <t>2026-05-29 09:46:28.835</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1779509220333</v>
+        <v>1780022787244</v>
       </c>
       <c r="C53" t="n">
-        <v>88046</v>
+        <v>74704</v>
       </c>
       <c r="D53" t="n">
-        <v>-29.58</v>
+        <v>-396.41</v>
       </c>
       <c r="E53" t="n">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="F53" t="n">
-        <v>705</v>
+        <v>200</v>
       </c>
       <c r="G53" t="n">
-        <v>234.42</v>
+        <v>370.08</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1590</v>
+      </c>
+      <c r="L53" t="n">
+        <v>109</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.406</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:04.695</t>
+          <t>2026-05-29 09:46:28.843</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1779509220534</v>
+        <v>1780022787444</v>
       </c>
       <c r="C54" t="n">
-        <v>88258</v>
+        <v>74707</v>
       </c>
       <c r="D54" t="n">
-        <v>183.9</v>
+        <v>-373.59</v>
       </c>
       <c r="E54" t="n">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="F54" t="n">
-        <v>705</v>
+        <v>200</v>
       </c>
       <c r="G54" t="n">
-        <v>234.42</v>
+        <v>370.08</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I54" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J54" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1399</v>
+      </c>
+      <c r="L54" t="n">
+        <v>106</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.537</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:04.696</t>
+          <t>2026-05-29 09:46:28.846</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1779509220736</v>
+        <v>1780022787644</v>
       </c>
       <c r="C55" t="n">
-        <v>88811</v>
+        <v>74430</v>
       </c>
       <c r="D55" t="n">
-        <v>727.71</v>
+        <v>-631.91</v>
       </c>
       <c r="E55" t="n">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="F55" t="n">
-        <v>543</v>
+        <v>200</v>
       </c>
       <c r="G55" t="n">
-        <v>238.91</v>
+        <v>370.08</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1201</v>
+      </c>
+      <c r="L55" t="n">
+        <v>105</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.332</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:05.054</t>
+          <t>2026-05-29 09:46:28.847</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1779509220937</v>
+        <v>1780022787844</v>
       </c>
       <c r="C56" t="n">
-        <v>88617</v>
+        <v>74349</v>
       </c>
       <c r="D56" t="n">
-        <v>497.32</v>
+        <v>-681.3099999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="F56" t="n">
-        <v>543</v>
+        <v>200</v>
       </c>
       <c r="G56" t="n">
-        <v>238.91</v>
+        <v>370.08</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1002</v>
+      </c>
+      <c r="L56" t="n">
+        <v>104</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.051</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:05.347</t>
+          <t>2026-05-29 09:46:29.809</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1779509221138</v>
+        <v>1780022788044</v>
       </c>
       <c r="C57" t="n">
-        <v>88687</v>
+        <v>74478</v>
       </c>
       <c r="D57" t="n">
-        <v>542.45</v>
+        <v>-518.25</v>
       </c>
       <c r="E57" t="n">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="F57" t="n">
-        <v>543</v>
+        <v>200</v>
       </c>
       <c r="G57" t="n">
-        <v>238.91</v>
+        <v>370.08</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1764</v>
+      </c>
+      <c r="L57" t="n">
+        <v>106</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.601</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:05.612</t>
+          <t>2026-05-29 09:46:29.828</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1779509221340</v>
+        <v>1780022788263</v>
       </c>
       <c r="C58" t="n">
-        <v>88801</v>
+        <v>74447</v>
       </c>
       <c r="D58" t="n">
-        <v>629.33</v>
+        <v>-523.34</v>
       </c>
       <c r="E58" t="n">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="F58" t="n">
-        <v>543</v>
+        <v>2258</v>
       </c>
       <c r="G58" t="n">
-        <v>238.91</v>
+        <v>370.08</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I58" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1564</v>
+      </c>
+      <c r="L58" t="n">
+        <v>118</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.389</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:05.619</t>
+          <t>2026-05-29 09:46:29.968</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1779509221541</v>
+        <v>1780022788463</v>
       </c>
       <c r="C59" t="n">
-        <v>88569</v>
+        <v>74375</v>
       </c>
       <c r="D59" t="n">
-        <v>365.87</v>
+        <v>-569.17</v>
       </c>
       <c r="E59" t="n">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="F59" t="n">
-        <v>543</v>
+        <v>2258</v>
       </c>
       <c r="G59" t="n">
-        <v>238.91</v>
+        <v>370.08</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J59" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1504</v>
+      </c>
+      <c r="L59" t="n">
+        <v>120</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.11</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:06.262</t>
+          <t>2026-05-29 09:46:29.969</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1779509221742</v>
+        <v>1780022788663</v>
       </c>
       <c r="C60" t="n">
-        <v>89237</v>
+        <v>74489</v>
       </c>
       <c r="D60" t="n">
-        <v>1015.57</v>
+        <v>-426.71</v>
       </c>
       <c r="E60" t="n">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="F60" t="n">
-        <v>543</v>
+        <v>2258</v>
       </c>
       <c r="G60" t="n">
-        <v>238.91</v>
+        <v>370.08</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J60" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1305</v>
+      </c>
+      <c r="L60" t="n">
+        <v>109</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.946</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:06.491</t>
+          <t>2026-05-29 09:46:29.970</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1779509221944</v>
+        <v>1780022788863</v>
       </c>
       <c r="C61" t="n">
-        <v>88515</v>
+        <v>74602</v>
       </c>
       <c r="D61" t="n">
-        <v>242.79</v>
+        <v>-292.37</v>
       </c>
       <c r="E61" t="n">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="F61" t="n">
-        <v>543</v>
+        <v>580</v>
       </c>
       <c r="G61" t="n">
-        <v>238.91</v>
+        <v>352.6</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J61" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1107</v>
+      </c>
+      <c r="L61" t="n">
+        <v>106</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.874</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:06.492</t>
+          <t>2026-05-29 09:46:29.971</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1779509222145</v>
+        <v>1780022789063</v>
       </c>
       <c r="C62" t="n">
-        <v>88657</v>
+        <v>74563</v>
       </c>
       <c r="D62" t="n">
-        <v>372.65</v>
+        <v>-316.76</v>
       </c>
       <c r="E62" t="n">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="F62" t="n">
-        <v>543</v>
+        <v>580</v>
       </c>
       <c r="G62" t="n">
-        <v>238.91</v>
+        <v>352.6</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I62" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J62" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K62" t="n">
+        <v>908</v>
+      </c>
+      <c r="L62" t="n">
+        <v>107</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.79</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:06.738</t>
+          <t>2026-05-29 09:46:30.668</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1779509222346</v>
+        <v>1780022789263</v>
       </c>
       <c r="C63" t="n">
-        <v>88285</v>
+        <v>74515</v>
       </c>
       <c r="D63" t="n">
-        <v>-17.98</v>
+        <v>-348.92</v>
       </c>
       <c r="E63" t="n">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="F63" t="n">
-        <v>543</v>
+        <v>580</v>
       </c>
       <c r="G63" t="n">
-        <v>238.91</v>
+        <v>352.6</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J63" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1404</v>
+      </c>
+      <c r="L63" t="n">
+        <v>98</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.962</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:06.740</t>
+          <t>2026-05-29 09:46:30.670</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1779509222548</v>
+        <v>1780022789463</v>
       </c>
       <c r="C64" t="n">
-        <v>88438</v>
+        <v>74824</v>
       </c>
       <c r="D64" t="n">
-        <v>135.92</v>
+        <v>-22.47</v>
       </c>
       <c r="E64" t="n">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="F64" t="n">
-        <v>543</v>
+        <v>580</v>
       </c>
       <c r="G64" t="n">
-        <v>238.91</v>
+        <v>352.6</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I64" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J64" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1206</v>
+      </c>
+      <c r="L64" t="n">
+        <v>119</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.123</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:06.742</t>
+          <t>2026-05-29 09:46:31.935</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1779509222749</v>
+        <v>1780022789663</v>
       </c>
       <c r="C65" t="n">
-        <v>88601</v>
+        <v>75052</v>
       </c>
       <c r="D65" t="n">
-        <v>292.12</v>
+        <v>206.65</v>
       </c>
       <c r="E65" t="n">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="F65" t="n">
-        <v>543</v>
+        <v>580</v>
       </c>
       <c r="G65" t="n">
-        <v>238.91</v>
+        <v>352.6</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J65" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K65" t="n">
+        <v>2271</v>
+      </c>
+      <c r="L65" t="n">
+        <v>114</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.507</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:07.015</t>
+          <t>2026-05-29 09:46:31.936</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1779509222950</v>
+        <v>1780022789882</v>
       </c>
       <c r="C66" t="n">
-        <v>88309</v>
+        <v>74985</v>
       </c>
       <c r="D66" t="n">
-        <v>-14.48</v>
+        <v>129.32</v>
       </c>
       <c r="E66" t="n">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="F66" t="n">
-        <v>2154</v>
+        <v>580</v>
       </c>
       <c r="G66" t="n">
-        <v>238.91</v>
+        <v>352.6</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K66" t="n">
+        <v>2053</v>
+      </c>
+      <c r="L66" t="n">
+        <v>106</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.505</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:07.308</t>
+          <t>2026-05-29 09:46:31.937</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1779509223151</v>
+        <v>1780022790082</v>
       </c>
       <c r="C67" t="n">
-        <v>88273</v>
+        <v>75169</v>
       </c>
       <c r="D67" t="n">
-        <v>-49.76</v>
+        <v>306.85</v>
       </c>
       <c r="E67" t="n">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="F67" t="n">
-        <v>2154</v>
+        <v>580</v>
       </c>
       <c r="G67" t="n">
-        <v>238.91</v>
+        <v>352.6</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1854</v>
+      </c>
+      <c r="L67" t="n">
+        <v>105</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.963</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:07.310</t>
+          <t>2026-05-29 09:46:31.942</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1779509223353</v>
+        <v>1780022790282</v>
       </c>
       <c r="C68" t="n">
-        <v>88253</v>
+        <v>74993</v>
       </c>
       <c r="D68" t="n">
-        <v>-67.27</v>
+        <v>115.51</v>
       </c>
       <c r="E68" t="n">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="F68" t="n">
-        <v>2154</v>
+        <v>580</v>
       </c>
       <c r="G68" t="n">
-        <v>238.91</v>
+        <v>352.6</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I68" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J68" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1660</v>
+      </c>
+      <c r="L68" t="n">
+        <v>113</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.609</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:07.764</t>
+          <t>2026-05-29 09:46:31.952</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1779509223554</v>
+        <v>1780022790482</v>
       </c>
       <c r="C69" t="n">
-        <v>87591</v>
+        <v>74882</v>
       </c>
       <c r="D69" t="n">
-        <v>-725.91</v>
+        <v>-1.27</v>
       </c>
       <c r="E69" t="n">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="F69" t="n">
-        <v>2154</v>
+        <v>580</v>
       </c>
       <c r="G69" t="n">
-        <v>238.91</v>
+        <v>352.6</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1469</v>
+      </c>
+      <c r="L69" t="n">
+        <v>103</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.968</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:08.055</t>
+          <t>2026-05-29 09:46:31.967</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1779509223755</v>
+        <v>1780022790682</v>
       </c>
       <c r="C70" t="n">
-        <v>87749</v>
+        <v>74879</v>
       </c>
       <c r="D70" t="n">
-        <v>-531.61</v>
+        <v>-4.2</v>
       </c>
       <c r="E70" t="n">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="F70" t="n">
-        <v>2154</v>
+        <v>580</v>
       </c>
       <c r="G70" t="n">
-        <v>238.91</v>
+        <v>352.6</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J70" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1284</v>
+      </c>
+      <c r="L70" t="n">
+        <v>105</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.525</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:08.647</t>
+          <t>2026-05-29 09:46:31.973</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1779509223957</v>
+        <v>1780022790882</v>
       </c>
       <c r="C71" t="n">
-        <v>87906</v>
+        <v>75943</v>
       </c>
       <c r="D71" t="n">
-        <v>-348.03</v>
+        <v>1060.01</v>
       </c>
       <c r="E71" t="n">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="F71" t="n">
-        <v>2154</v>
+        <v>2059</v>
       </c>
       <c r="G71" t="n">
-        <v>238.91</v>
+        <v>352.6</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I71" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J71" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1091</v>
+      </c>
+      <c r="L71" t="n">
+        <v>105</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.457</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:08.913</t>
+          <t>2026-05-29 09:46:32.372</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1779509224158</v>
+        <v>1780022791082</v>
       </c>
       <c r="C72" t="n">
-        <v>87911</v>
+        <v>76675</v>
       </c>
       <c r="D72" t="n">
-        <v>-325.63</v>
+        <v>1739.01</v>
       </c>
       <c r="E72" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F72" t="n">
-        <v>1309</v>
+        <v>2059</v>
       </c>
       <c r="G72" t="n">
-        <v>308.93</v>
+        <v>352.6</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I72" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J72" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1290</v>
+      </c>
+      <c r="L72" t="n">
+        <v>119</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.651</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:08.915</t>
+          <t>2026-05-29 09:46:32.380</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1779509224359</v>
+        <v>1780022791301</v>
       </c>
       <c r="C73" t="n">
-        <v>87851</v>
+        <v>76828</v>
       </c>
       <c r="D73" t="n">
-        <v>-369.35</v>
+        <v>1805.06</v>
       </c>
       <c r="E73" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F73" t="n">
-        <v>1309</v>
+        <v>2059</v>
       </c>
       <c r="G73" t="n">
-        <v>308.93</v>
+        <v>352.6</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J73" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1078</v>
+      </c>
+      <c r="L73" t="n">
+        <v>115</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1.038</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:08.916</t>
+          <t>2026-05-29 09:46:32.695</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1779509224561</v>
+        <v>1780022791501</v>
       </c>
       <c r="C74" t="n">
-        <v>87970</v>
+        <v>76928</v>
       </c>
       <c r="D74" t="n">
-        <v>-231.88</v>
+        <v>1814.8</v>
       </c>
       <c r="E74" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F74" t="n">
-        <v>1309</v>
+        <v>2059</v>
       </c>
       <c r="G74" t="n">
-        <v>308.93</v>
+        <v>352.6</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I74" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1193</v>
+      </c>
+      <c r="L74" t="n">
+        <v>114</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1.368</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:09.250</t>
+          <t>2026-05-29 09:46:32.746</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1779509224762</v>
+        <v>1780022791701</v>
       </c>
       <c r="C75" t="n">
-        <v>87819</v>
+        <v>79915</v>
       </c>
       <c r="D75" t="n">
-        <v>-371.29</v>
+        <v>4711.06</v>
       </c>
       <c r="E75" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="F75" t="n">
-        <v>544</v>
+        <v>2059</v>
       </c>
       <c r="G75" t="n">
-        <v>314.78</v>
+        <v>352.6</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1043</v>
+      </c>
+      <c r="L75" t="n">
+        <v>116</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.729</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:09.519</t>
+          <t>2026-05-29 09:46:33.175</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1779509224963</v>
+        <v>1780022791901</v>
       </c>
       <c r="C76" t="n">
-        <v>88160</v>
+        <v>79674</v>
       </c>
       <c r="D76" t="n">
-        <v>-11.72</v>
+        <v>4234.51</v>
       </c>
       <c r="E76" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="F76" t="n">
-        <v>544</v>
+        <v>2059</v>
       </c>
       <c r="G76" t="n">
-        <v>314.78</v>
+        <v>352.6</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1273</v>
+      </c>
+      <c r="L76" t="n">
+        <v>116</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.849</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:09.520</t>
+          <t>2026-05-29 09:46:33.176</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1779509225165</v>
+        <v>1780022792101</v>
       </c>
       <c r="C77" t="n">
-        <v>88656</v>
+        <v>79356</v>
       </c>
       <c r="D77" t="n">
-        <v>484.86</v>
+        <v>3704.79</v>
       </c>
       <c r="E77" t="n">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="F77" t="n">
-        <v>422</v>
+        <v>2059</v>
       </c>
       <c r="G77" t="n">
-        <v>326.34</v>
+        <v>352.6</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J77" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1074</v>
+      </c>
+      <c r="L77" t="n">
+        <v>124</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.572</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:09.521</t>
+          <t>2026-05-29 09:46:34.681</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1779509225366</v>
+        <v>1780022792301</v>
       </c>
       <c r="C78" t="n">
-        <v>88305</v>
+        <v>78370</v>
       </c>
       <c r="D78" t="n">
-        <v>109.62</v>
+        <v>2533.55</v>
       </c>
       <c r="E78" t="n">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="F78" t="n">
-        <v>422</v>
+        <v>2059</v>
       </c>
       <c r="G78" t="n">
-        <v>326.34</v>
+        <v>352.6</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J78" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K78" t="n">
+        <v>2380</v>
+      </c>
+      <c r="L78" t="n">
+        <v>115</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.5590000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:10.085</t>
+          <t>2026-05-29 09:46:34.682</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1779509225567</v>
+        <v>1780022792501</v>
       </c>
       <c r="C79" t="n">
-        <v>88140</v>
+        <v>77652</v>
       </c>
       <c r="D79" t="n">
-        <v>-60.86</v>
+        <v>1688.87</v>
       </c>
       <c r="E79" t="n">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="F79" t="n">
-        <v>422</v>
+        <v>2059</v>
       </c>
       <c r="G79" t="n">
-        <v>326.34</v>
+        <v>352.6</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I79" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J79" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K79" t="n">
+        <v>2181</v>
+      </c>
+      <c r="L79" t="n">
+        <v>112</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.59</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:10.343</t>
+          <t>2026-05-29 09:46:34.684</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1779509225769</v>
+        <v>1780022792702</v>
       </c>
       <c r="C80" t="n">
-        <v>87959</v>
+        <v>76956</v>
       </c>
       <c r="D80" t="n">
-        <v>-238.82</v>
+        <v>908.4299999999999</v>
       </c>
       <c r="E80" t="n">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="F80" t="n">
-        <v>422</v>
+        <v>2059</v>
       </c>
       <c r="G80" t="n">
-        <v>326.34</v>
+        <v>352.6</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I80" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J80" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1981</v>
+      </c>
+      <c r="L80" t="n">
+        <v>109</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.61</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:10.345</t>
+          <t>2026-05-29 09:46:34.691</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1779509225970</v>
+        <v>1780022792901</v>
       </c>
       <c r="C81" t="n">
-        <v>88169</v>
+        <v>76771</v>
       </c>
       <c r="D81" t="n">
-        <v>-16.88</v>
+        <v>678</v>
       </c>
       <c r="E81" t="n">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="F81" t="n">
-        <v>422</v>
+        <v>2059</v>
       </c>
       <c r="G81" t="n">
-        <v>326.34</v>
+        <v>352.6</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J81" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1790</v>
+      </c>
+      <c r="L81" t="n">
+        <v>126</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.521</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:10.346</t>
+          <t>2026-05-29 09:46:34.736</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1779509226171</v>
+        <v>1780022793120</v>
       </c>
       <c r="C82" t="n">
-        <v>88204</v>
+        <v>76302</v>
       </c>
       <c r="D82" t="n">
-        <v>18.97</v>
+        <v>175.1</v>
       </c>
       <c r="E82" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="F82" t="n">
-        <v>926</v>
+        <v>2059</v>
       </c>
       <c r="G82" t="n">
-        <v>261.54</v>
+        <v>352.6</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1615</v>
+      </c>
+      <c r="L82" t="n">
+        <v>116</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.791</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:10.583</t>
+          <t>2026-05-29 09:46:34.737</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1779509226372</v>
+        <v>1780022793320</v>
       </c>
       <c r="C83" t="n">
-        <v>88228</v>
+        <v>76195</v>
       </c>
       <c r="D83" t="n">
-        <v>42.02</v>
+        <v>59.35</v>
       </c>
       <c r="E83" t="n">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="F83" t="n">
-        <v>282</v>
+        <v>2059</v>
       </c>
       <c r="G83" t="n">
-        <v>285.14</v>
+        <v>352.6</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1416</v>
+      </c>
+      <c r="L83" t="n">
+        <v>115</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.887</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:10.583</t>
+          <t>2026-05-29 09:46:35.231</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1779509226574</v>
+        <v>1780022793520</v>
       </c>
       <c r="C84" t="n">
-        <v>87877</v>
+        <v>76865</v>
       </c>
       <c r="D84" t="n">
-        <v>-311.08</v>
+        <v>726.38</v>
       </c>
       <c r="E84" t="n">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="F84" t="n">
-        <v>282</v>
+        <v>2059</v>
       </c>
       <c r="G84" t="n">
-        <v>285.14</v>
+        <v>352.6</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J84" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1710</v>
+      </c>
+      <c r="L84" t="n">
+        <v>111</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.642</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:10.868</t>
+          <t>2026-05-29 09:46:35.240</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1779509226775</v>
+        <v>1780022793720</v>
       </c>
       <c r="C85" t="n">
-        <v>87890</v>
+        <v>76712</v>
       </c>
       <c r="D85" t="n">
-        <v>-282.53</v>
+        <v>537.0599999999999</v>
       </c>
       <c r="E85" t="n">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="F85" t="n">
-        <v>282</v>
+        <v>2059</v>
       </c>
       <c r="G85" t="n">
-        <v>285.14</v>
+        <v>352.6</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I85" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J85" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1519</v>
+      </c>
+      <c r="L85" t="n">
+        <v>118</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.183</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:11.133</t>
+          <t>2026-05-29 09:46:35.279</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1779509226976</v>
+        <v>1780022793921</v>
       </c>
       <c r="C86" t="n">
-        <v>87843</v>
+        <v>76802</v>
       </c>
       <c r="D86" t="n">
-        <v>-315.4</v>
+        <v>600.21</v>
       </c>
       <c r="E86" t="n">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="F86" t="n">
-        <v>282</v>
+        <v>2059</v>
       </c>
       <c r="G86" t="n">
-        <v>285.14</v>
+        <v>352.6</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1357</v>
+      </c>
+      <c r="L86" t="n">
+        <v>108</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.9360000000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:11.517</t>
+          <t>2026-05-29 09:46:35.281</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1779509227178</v>
+        <v>1780022794121</v>
       </c>
       <c r="C87" t="n">
-        <v>87939</v>
+        <v>76517</v>
       </c>
       <c r="D87" t="n">
-        <v>-203.63</v>
+        <v>285.2</v>
       </c>
       <c r="E87" t="n">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="F87" t="n">
-        <v>282</v>
+        <v>2059</v>
       </c>
       <c r="G87" t="n">
-        <v>285.14</v>
+        <v>352.6</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I87" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="J87" t="n">
+        <v>35.76</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1160</v>
+      </c>
+      <c r="L87" t="n">
+        <v>106</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:11.784</t>
+          <t>2026-05-29 09:46:35.428</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1779509227379</v>
+        <v>1780022794320</v>
       </c>
       <c r="C88" t="n">
-        <v>87297</v>
+        <v>76327</v>
       </c>
       <c r="D88" t="n">
-        <v>-835.45</v>
+        <v>80.94</v>
       </c>
       <c r="E88" t="n">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="F88" t="n">
-        <v>926</v>
+        <v>2059</v>
       </c>
       <c r="G88" t="n">
-        <v>297.38</v>
+        <v>352.6</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J88" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1107</v>
+      </c>
+      <c r="L88" t="n">
+        <v>129</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.598</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:11.786</t>
+          <t>2026-05-29 09:46:35.429</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1779509227580</v>
+        <v>1780022794521</v>
       </c>
       <c r="C89" t="n">
-        <v>87766</v>
+        <v>76107</v>
       </c>
       <c r="D89" t="n">
-        <v>-324.68</v>
+        <v>-143.11</v>
       </c>
       <c r="E89" t="n">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="F89" t="n">
-        <v>926</v>
+        <v>2059</v>
       </c>
       <c r="G89" t="n">
-        <v>297.38</v>
+        <v>352.6</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K89" t="n">
+        <v>907</v>
+      </c>
+      <c r="L89" t="n">
+        <v>105</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.507</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:12.068</t>
+          <t>2026-05-29 09:46:35.840</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1779509227782</v>
+        <v>1780022794740</v>
       </c>
       <c r="C90" t="n">
-        <v>87694</v>
+        <v>76270</v>
       </c>
       <c r="D90" t="n">
-        <v>-380.44</v>
+        <v>27.05</v>
       </c>
       <c r="E90" t="n">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="F90" t="n">
-        <v>504</v>
+        <v>2059</v>
       </c>
       <c r="G90" t="n">
-        <v>300.67</v>
+        <v>352.6</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="J90" t="n">
+        <v>35.78</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L90" t="n">
+        <v>138</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.836</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:12.075</t>
+          <t>2026-05-29 09:46:35.842</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1779509227983</v>
+        <v>1780022794939</v>
       </c>
       <c r="C91" t="n">
-        <v>87707</v>
+        <v>76394</v>
       </c>
       <c r="D91" t="n">
-        <v>-348.42</v>
+        <v>149.69</v>
       </c>
       <c r="E91" t="n">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="F91" t="n">
-        <v>504</v>
+        <v>2059</v>
       </c>
       <c r="G91" t="n">
-        <v>300.67</v>
+        <v>352.6</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K91" t="n">
+        <v>902</v>
+      </c>
+      <c r="L91" t="n">
+        <v>123</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:12.620</t>
+          <t>2026-05-29 09:46:36.443</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1779509228184</v>
+        <v>1780022795140</v>
       </c>
       <c r="C92" t="n">
-        <v>87849</v>
+        <v>76316</v>
       </c>
       <c r="D92" t="n">
-        <v>-189</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="E92" t="n">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="F92" t="n">
-        <v>504</v>
+        <v>4097</v>
       </c>
       <c r="G92" t="n">
-        <v>300.67</v>
+        <v>352.6</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1303</v>
+      </c>
+      <c r="L92" t="n">
+        <v>162</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.678</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:12.895</t>
+          <t>2026-05-29 09:46:36.463</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1779509228386</v>
+        <v>1780022795339</v>
       </c>
       <c r="C93" t="n">
-        <v>87855</v>
+        <v>76770</v>
       </c>
       <c r="D93" t="n">
-        <v>-173.55</v>
+        <v>515</v>
       </c>
       <c r="E93" t="n">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="F93" t="n">
-        <v>504</v>
+        <v>4097</v>
       </c>
       <c r="G93" t="n">
-        <v>300.67</v>
+        <v>352.6</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1123</v>
+      </c>
+      <c r="L93" t="n">
+        <v>109</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.571</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:12.897</t>
+          <t>2026-05-29 09:46:36.464</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1779509228587</v>
+        <v>1780022795540</v>
       </c>
       <c r="C94" t="n">
-        <v>87448</v>
+        <v>76862</v>
       </c>
       <c r="D94" t="n">
-        <v>-571.87</v>
+        <v>581.25</v>
       </c>
       <c r="E94" t="n">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="F94" t="n">
-        <v>504</v>
+        <v>4097</v>
       </c>
       <c r="G94" t="n">
-        <v>300.67</v>
+        <v>352.6</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I94" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K94" t="n">
+        <v>923</v>
+      </c>
+      <c r="L94" t="n">
+        <v>105</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.555</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:12.897</t>
+          <t>2026-05-29 09:46:36.834</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1779509228788</v>
+        <v>1780022795739</v>
       </c>
       <c r="C95" t="n">
-        <v>87551</v>
+        <v>76544</v>
       </c>
       <c r="D95" t="n">
-        <v>-440.28</v>
+        <v>234.19</v>
       </c>
       <c r="E95" t="n">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="F95" t="n">
-        <v>504</v>
+        <v>4097</v>
       </c>
       <c r="G95" t="n">
-        <v>300.67</v>
+        <v>352.6</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J95" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1094</v>
+      </c>
+      <c r="L95" t="n">
+        <v>119</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1.056</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:13.148</t>
+          <t>2026-05-29 09:46:36.836</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1779509228990</v>
+        <v>1780022795939</v>
       </c>
       <c r="C96" t="n">
-        <v>87493</v>
+        <v>76586</v>
       </c>
       <c r="D96" t="n">
-        <v>-476.27</v>
+        <v>264.48</v>
       </c>
       <c r="E96" t="n">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="F96" t="n">
-        <v>504</v>
+        <v>4097</v>
       </c>
       <c r="G96" t="n">
-        <v>300.67</v>
+        <v>352.6</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K96" t="n">
+        <v>896</v>
+      </c>
+      <c r="L96" t="n">
+        <v>111</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1.051</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:13.150</t>
+          <t>2026-05-29 09:46:37.145</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1779509229191</v>
+        <v>1780022796139</v>
       </c>
       <c r="C97" t="n">
-        <v>87459</v>
+        <v>76713</v>
       </c>
       <c r="D97" t="n">
-        <v>-486.45</v>
+        <v>378.25</v>
       </c>
       <c r="E97" t="n">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="F97" t="n">
-        <v>504</v>
+        <v>1160</v>
       </c>
       <c r="G97" t="n">
-        <v>300.67</v>
+        <v>361.18</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I97" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="J97" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1004</v>
+      </c>
+      <c r="L97" t="n">
+        <v>112</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.538</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:13.742</t>
+          <t>2026-05-29 09:46:37.161</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1779509229392</v>
+        <v>1780022796339</v>
       </c>
       <c r="C98" t="n">
-        <v>87352</v>
+        <v>76636</v>
       </c>
       <c r="D98" t="n">
-        <v>-569.13</v>
+        <v>282.34</v>
       </c>
       <c r="E98" t="n">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="F98" t="n">
-        <v>504</v>
+        <v>1160</v>
       </c>
       <c r="G98" t="n">
-        <v>300.67</v>
+        <v>361.18</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I98" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J98" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K98" t="n">
+        <v>820</v>
+      </c>
+      <c r="L98" t="n">
+        <v>106</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.198</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:14.042</t>
+          <t>2026-05-29 09:46:38.274</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1779509229594</v>
+        <v>1780022796558</v>
       </c>
       <c r="C99" t="n">
-        <v>87086</v>
+        <v>76916</v>
       </c>
       <c r="D99" t="n">
-        <v>-806.67</v>
+        <v>548.22</v>
       </c>
       <c r="E99" t="n">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="F99" t="n">
-        <v>504</v>
+        <v>1160</v>
       </c>
       <c r="G99" t="n">
-        <v>300.67</v>
+        <v>361.18</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I99" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J99" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1714</v>
+      </c>
+      <c r="L99" t="n">
+        <v>112</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1.146</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:14.043</t>
+          <t>2026-05-29 09:46:38.275</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1779509229795</v>
+        <v>1780022796758</v>
       </c>
       <c r="C100" t="n">
-        <v>87550</v>
+        <v>77192</v>
       </c>
       <c r="D100" t="n">
-        <v>-302.34</v>
+        <v>796.8099999999999</v>
       </c>
       <c r="E100" t="n">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="F100" t="n">
-        <v>504</v>
+        <v>1160</v>
       </c>
       <c r="G100" t="n">
-        <v>300.67</v>
+        <v>361.18</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I100" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J100" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1516</v>
+      </c>
+      <c r="L100" t="n">
+        <v>108</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.952</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:14.649</t>
+          <t>2026-05-29 09:46:38.276</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1779509229996</v>
+        <v>1780022796958</v>
       </c>
       <c r="C101" t="n">
-        <v>86917</v>
+        <v>76989</v>
       </c>
       <c r="D101" t="n">
-        <v>-920.22</v>
+        <v>553.97</v>
       </c>
       <c r="E101" t="n">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="F101" t="n">
-        <v>2154</v>
+        <v>1160</v>
       </c>
       <c r="G101" t="n">
-        <v>300.67</v>
+        <v>361.18</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I101" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J101" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1317</v>
+      </c>
+      <c r="L101" t="n">
+        <v>107</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.9379999999999999</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:14.894</t>
+          <t>2026-05-29 09:46:38.648</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1779509230198</v>
+        <v>1780022797158</v>
       </c>
       <c r="C102" t="n">
-        <v>87008</v>
+        <v>76950</v>
       </c>
       <c r="D102" t="n">
-        <v>-783.21</v>
+        <v>487.27</v>
       </c>
       <c r="E102" t="n">
+        <v>62</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1160</v>
+      </c>
+      <c r="G102" t="n">
+        <v>361.18</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J102" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1490</v>
+      </c>
+      <c r="L102" t="n">
         <v>114</v>
       </c>
-      <c r="F102" t="n">
-        <v>2154</v>
-      </c>
-      <c r="G102" t="n">
-        <v>300.67</v>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
+      <c r="M102" t="n">
+        <v>0.726</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:14.899</t>
+          <t>2026-05-29 09:46:38.650</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1779509230399</v>
+        <v>1780022797358</v>
       </c>
       <c r="C103" t="n">
-        <v>87108</v>
+        <v>77236</v>
       </c>
       <c r="D103" t="n">
-        <v>-644.05</v>
+        <v>748.91</v>
       </c>
       <c r="E103" t="n">
+        <v>63</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1219</v>
+      </c>
+      <c r="G103" t="n">
+        <v>373.49</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="J103" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1291</v>
+      </c>
+      <c r="L103" t="n">
         <v>114</v>
       </c>
-      <c r="F103" t="n">
-        <v>2154</v>
-      </c>
-      <c r="G103" t="n">
-        <v>300.67</v>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
+      <c r="M103" t="n">
+        <v>0.845</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:14.926</t>
+          <t>2026-05-29 09:46:38.651</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1779509230600</v>
+        <v>1780022797558</v>
       </c>
       <c r="C104" t="n">
-        <v>86886</v>
+        <v>77487</v>
       </c>
       <c r="D104" t="n">
-        <v>-833.85</v>
+        <v>962.46</v>
       </c>
       <c r="E104" t="n">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="F104" t="n">
-        <v>684</v>
+        <v>1219</v>
       </c>
       <c r="G104" t="n">
-        <v>300.06</v>
+        <v>373.49</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I104" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J104" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1092</v>
+      </c>
+      <c r="L104" t="n">
+        <v>114</v>
+      </c>
+      <c r="M104" t="n">
+        <v>1.154</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:15.171</t>
+          <t>2026-05-29 09:46:38.652</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1779509230802</v>
+        <v>1780022797758</v>
       </c>
       <c r="C105" t="n">
-        <v>87064</v>
+        <v>77587</v>
       </c>
       <c r="D105" t="n">
-        <v>-614.16</v>
+        <v>1014.34</v>
       </c>
       <c r="E105" t="n">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="F105" t="n">
-        <v>684</v>
+        <v>1219</v>
       </c>
       <c r="G105" t="n">
-        <v>300.06</v>
+        <v>373.49</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I105" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J105" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K105" t="n">
+        <v>893</v>
+      </c>
+      <c r="L105" t="n">
+        <v>116</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.9340000000000001</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:15.177</t>
+          <t>2026-05-29 09:46:38.887</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1779509231003</v>
+        <v>1780022797958</v>
       </c>
       <c r="C106" t="n">
-        <v>87303</v>
+        <v>77666</v>
       </c>
       <c r="D106" t="n">
-        <v>-344.45</v>
+        <v>1042.62</v>
       </c>
       <c r="E106" t="n">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="F106" t="n">
-        <v>684</v>
+        <v>1219</v>
       </c>
       <c r="G106" t="n">
-        <v>300.06</v>
+        <v>373.49</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I106" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J106" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K106" t="n">
+        <v>928</v>
+      </c>
+      <c r="L106" t="n">
+        <v>113</v>
+      </c>
+      <c r="M106" t="n">
+        <v>1.131</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:15.204</t>
+          <t>2026-05-29 09:46:38.888</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1779509231204</v>
+        <v>1780022798177</v>
       </c>
       <c r="C107" t="n">
-        <v>87311</v>
+        <v>77656</v>
       </c>
       <c r="D107" t="n">
-        <v>-319.23</v>
+        <v>980.49</v>
       </c>
       <c r="E107" t="n">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="F107" t="n">
-        <v>423</v>
+        <v>1219</v>
       </c>
       <c r="G107" t="n">
-        <v>310.97</v>
+        <v>373.49</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I107" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J107" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K107" t="n">
+        <v>710</v>
+      </c>
+      <c r="L107" t="n">
+        <v>111</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.878</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:15.818</t>
+          <t>2026-05-29 09:46:40.837</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1779509231406</v>
+        <v>1780022798377</v>
       </c>
       <c r="C108" t="n">
-        <v>87149</v>
+        <v>77684</v>
       </c>
       <c r="D108" t="n">
-        <v>-465.26</v>
+        <v>959.47</v>
       </c>
       <c r="E108" t="n">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="F108" t="n">
-        <v>423</v>
+        <v>1219</v>
       </c>
       <c r="G108" t="n">
-        <v>310.97</v>
+        <v>373.49</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I108" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J108" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K108" t="n">
+        <v>2458</v>
+      </c>
+      <c r="L108" t="n">
+        <v>111</v>
+      </c>
+      <c r="M108" t="n">
+        <v>1.006</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:16.062</t>
+          <t>2026-05-29 09:46:40.838</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1779509231607</v>
+        <v>1780022798577</v>
       </c>
       <c r="C109" t="n">
-        <v>87366</v>
+        <v>77991</v>
       </c>
       <c r="D109" t="n">
-        <v>-225</v>
+        <v>1218.49</v>
       </c>
       <c r="E109" t="n">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="F109" t="n">
-        <v>423</v>
+        <v>1219</v>
       </c>
       <c r="G109" t="n">
-        <v>310.97</v>
+        <v>373.49</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I109" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J109" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K109" t="n">
+        <v>2260</v>
+      </c>
+      <c r="L109" t="n">
+        <v>111</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:16.063</t>
+          <t>2026-05-29 09:46:40.838</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1779509231808</v>
+        <v>1780022798777</v>
       </c>
       <c r="C110" t="n">
-        <v>87571</v>
+        <v>78080</v>
       </c>
       <c r="D110" t="n">
-        <v>-8.75</v>
+        <v>1246.57</v>
       </c>
       <c r="E110" t="n">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="F110" t="n">
-        <v>644</v>
+        <v>1219</v>
       </c>
       <c r="G110" t="n">
-        <v>308.51</v>
+        <v>373.49</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I110" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J110" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K110" t="n">
+        <v>2061</v>
+      </c>
+      <c r="L110" t="n">
+        <v>115</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0.706</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:16.346</t>
+          <t>2026-05-29 09:46:40.839</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1779509232010</v>
+        <v>1780022798977</v>
       </c>
       <c r="C111" t="n">
-        <v>87194</v>
+        <v>78263</v>
       </c>
       <c r="D111" t="n">
-        <v>-385.31</v>
+        <v>1367.24</v>
       </c>
       <c r="E111" t="n">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="F111" t="n">
-        <v>644</v>
+        <v>1219</v>
       </c>
       <c r="G111" t="n">
-        <v>308.51</v>
+        <v>373.49</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J111" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1862</v>
+      </c>
+      <c r="L111" t="n">
+        <v>112</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.57</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:16.459</t>
+          <t>2026-05-29 09:46:40.840</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1779509232211</v>
+        <v>1780022799177</v>
       </c>
       <c r="C112" t="n">
-        <v>87383</v>
+        <v>78554</v>
       </c>
       <c r="D112" t="n">
-        <v>-177.05</v>
+        <v>1589.88</v>
       </c>
       <c r="E112" t="n">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="F112" t="n">
-        <v>644</v>
+        <v>1219</v>
       </c>
       <c r="G112" t="n">
-        <v>308.51</v>
+        <v>373.49</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I112" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J112" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1663</v>
+      </c>
+      <c r="L112" t="n">
+        <v>114</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.507</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:16.756</t>
+          <t>2026-05-29 09:46:40.841</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1779509232412</v>
+        <v>1780022799377</v>
       </c>
       <c r="C113" t="n">
-        <v>87609</v>
+        <v>78613</v>
       </c>
       <c r="D113" t="n">
-        <v>57.8</v>
+        <v>1569.39</v>
       </c>
       <c r="E113" t="n">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="F113" t="n">
-        <v>725</v>
+        <v>1219</v>
       </c>
       <c r="G113" t="n">
-        <v>214.22</v>
+        <v>373.49</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I113" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J113" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1463</v>
+      </c>
+      <c r="L113" t="n">
+        <v>107</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.516</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:17.018</t>
+          <t>2026-05-29 09:46:41.235</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1779509232614</v>
+        <v>1780022799577</v>
       </c>
       <c r="C114" t="n">
-        <v>87593</v>
+        <v>78187</v>
       </c>
       <c r="D114" t="n">
-        <v>38.91</v>
+        <v>1064.92</v>
       </c>
       <c r="E114" t="n">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="F114" t="n">
-        <v>725</v>
+        <v>1219</v>
       </c>
       <c r="G114" t="n">
-        <v>214.22</v>
+        <v>373.49</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I114" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J114" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1656</v>
+      </c>
+      <c r="L114" t="n">
+        <v>108</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1.045</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:17.019</t>
+          <t>2026-05-29 09:46:41.236</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1779509232815</v>
+        <v>1780022799796</v>
       </c>
       <c r="C115" t="n">
-        <v>87345</v>
+        <v>78244</v>
       </c>
       <c r="D115" t="n">
-        <v>-211.03</v>
+        <v>1068.67</v>
       </c>
       <c r="E115" t="n">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="F115" t="n">
-        <v>725</v>
+        <v>1219</v>
       </c>
       <c r="G115" t="n">
-        <v>214.22</v>
+        <v>373.49</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I115" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J115" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1439</v>
+      </c>
+      <c r="L115" t="n">
+        <v>116</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0.98</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:17.296</t>
+          <t>2026-05-29 09:46:41.237</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1779509233016</v>
+        <v>1780022799996</v>
       </c>
       <c r="C116" t="n">
-        <v>87530</v>
+        <v>78413</v>
       </c>
       <c r="D116" t="n">
-        <v>-15.48</v>
+        <v>1184.24</v>
       </c>
       <c r="E116" t="n">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="F116" t="n">
-        <v>725</v>
+        <v>1219</v>
       </c>
       <c r="G116" t="n">
-        <v>214.22</v>
+        <v>373.49</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I116" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J116" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1240</v>
+      </c>
+      <c r="L116" t="n">
+        <v>112</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1.054</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:17.297</t>
+          <t>2026-05-29 09:46:41.799</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1779509233218</v>
+        <v>1780022800196</v>
       </c>
       <c r="C117" t="n">
-        <v>87709</v>
+        <v>78393</v>
       </c>
       <c r="D117" t="n">
-        <v>164.29</v>
+        <v>1105.03</v>
       </c>
       <c r="E117" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="F117" t="n">
-        <v>745</v>
+        <v>2718</v>
       </c>
       <c r="G117" t="n">
-        <v>216.96</v>
+        <v>373.49</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I117" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J117" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1602</v>
+      </c>
+      <c r="L117" t="n">
+        <v>108</v>
+      </c>
+      <c r="M117" t="n">
+        <v>1.434</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:17.560</t>
+          <t>2026-05-29 09:46:41.801</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1779509233419</v>
+        <v>1780022800496</v>
       </c>
       <c r="C118" t="n">
-        <v>87321</v>
+        <v>81467</v>
       </c>
       <c r="D118" t="n">
-        <v>-231.92</v>
+        <v>4123.77</v>
       </c>
       <c r="E118" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="F118" t="n">
-        <v>745</v>
+        <v>2718</v>
       </c>
       <c r="G118" t="n">
-        <v>216.96</v>
+        <v>373.49</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I118" t="n">
+        <v>62.62</v>
+      </c>
+      <c r="J118" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1304</v>
+      </c>
+      <c r="L118" t="n">
+        <v>122</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.997</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:17.572</t>
+          <t>2026-05-29 09:46:41.821</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1779509233620</v>
+        <v>1780022800696</v>
       </c>
       <c r="C119" t="n">
-        <v>87463</v>
+        <v>80163</v>
       </c>
       <c r="D119" t="n">
-        <v>-78.31999999999999</v>
+        <v>2613.59</v>
       </c>
       <c r="E119" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="F119" t="n">
-        <v>745</v>
+        <v>2718</v>
       </c>
       <c r="G119" t="n">
-        <v>216.96</v>
+        <v>373.49</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I119" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J119" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1124</v>
+      </c>
+      <c r="L119" t="n">
+        <v>117</v>
+      </c>
+      <c r="M119" t="n">
+        <v>1.457</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:18.067</t>
+          <t>2026-05-29 09:46:42.667</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1779509233822</v>
+        <v>1780022800896</v>
       </c>
       <c r="C120" t="n">
-        <v>87584</v>
+        <v>79166</v>
       </c>
       <c r="D120" t="n">
-        <v>46.59</v>
+        <v>1485.91</v>
       </c>
       <c r="E120" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="F120" t="n">
-        <v>745</v>
+        <v>2718</v>
       </c>
       <c r="G120" t="n">
-        <v>216.96</v>
+        <v>373.49</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I120" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J120" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1770</v>
+      </c>
+      <c r="L120" t="n">
+        <v>120</v>
+      </c>
+      <c r="M120" t="n">
+        <v>1.12</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:18.340</t>
+          <t>2026-05-29 09:46:42.669</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1779509234023</v>
+        <v>1780022801096</v>
       </c>
       <c r="C121" t="n">
-        <v>87404</v>
+        <v>79924</v>
       </c>
       <c r="D121" t="n">
-        <v>-135.74</v>
+        <v>2169.61</v>
       </c>
       <c r="E121" t="n">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="F121" t="n">
-        <v>765</v>
+        <v>2718</v>
       </c>
       <c r="G121" t="n">
-        <v>207.67</v>
+        <v>373.49</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I121" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J121" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K121" t="n">
+        <v>1572</v>
+      </c>
+      <c r="L121" t="n">
+        <v>121</v>
+      </c>
+      <c r="M121" t="n">
+        <v>1.077</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:18.581</t>
+          <t>2026-05-29 09:46:43.028</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1779509234224</v>
+        <v>1780022801297</v>
       </c>
       <c r="C122" t="n">
-        <v>87447</v>
+        <v>79876</v>
       </c>
       <c r="D122" t="n">
-        <v>-85.95</v>
+        <v>2013.13</v>
       </c>
       <c r="E122" t="n">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="F122" t="n">
-        <v>765</v>
+        <v>2718</v>
       </c>
       <c r="G122" t="n">
-        <v>207.67</v>
+        <v>373.49</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I122" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="J122" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1730</v>
+      </c>
+      <c r="L122" t="n">
+        <v>106</v>
+      </c>
+      <c r="M122" t="n">
+        <v>1.562</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:18.582</t>
+          <t>2026-05-29 09:46:43.036</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1779509234426</v>
+        <v>1780022801515</v>
       </c>
       <c r="C123" t="n">
-        <v>87570</v>
+        <v>81015</v>
       </c>
       <c r="D123" t="n">
-        <v>41.35</v>
+        <v>3051.47</v>
       </c>
       <c r="E123" t="n">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="F123" t="n">
-        <v>765</v>
+        <v>2718</v>
       </c>
       <c r="G123" t="n">
-        <v>207.67</v>
+        <v>373.49</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I123" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J123" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1521</v>
+      </c>
+      <c r="L123" t="n">
+        <v>107</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.569</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:18.584</t>
+          <t>2026-05-29 09:46:43.037</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1779509234627</v>
+        <v>1780022801715</v>
       </c>
       <c r="C124" t="n">
-        <v>87748</v>
+        <v>80688</v>
       </c>
       <c r="D124" t="n">
-        <v>217.28</v>
+        <v>2571.9</v>
       </c>
       <c r="E124" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="F124" t="n">
-        <v>624</v>
+        <v>2718</v>
       </c>
       <c r="G124" t="n">
-        <v>185.9</v>
+        <v>373.49</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I124" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J124" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1321</v>
+      </c>
+      <c r="L124" t="n">
+        <v>113</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.468</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:18.888</t>
+          <t>2026-05-29 09:46:43.038</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1779509234828</v>
+        <v>1780022801915</v>
       </c>
       <c r="C125" t="n">
-        <v>87383</v>
+        <v>80406</v>
       </c>
       <c r="D125" t="n">
-        <v>-158.58</v>
+        <v>2161.3</v>
       </c>
       <c r="E125" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="F125" t="n">
-        <v>624</v>
+        <v>2718</v>
       </c>
       <c r="G125" t="n">
-        <v>185.9</v>
+        <v>373.49</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I125" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J125" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1122</v>
+      </c>
+      <c r="L125" t="n">
+        <v>110</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.501</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:19.137</t>
+          <t>2026-05-29 09:46:43.431</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1779509235030</v>
+        <v>1780022802116</v>
       </c>
       <c r="C126" t="n">
-        <v>87522</v>
+        <v>78269</v>
       </c>
       <c r="D126" t="n">
-        <v>-11.66</v>
+        <v>-83.76000000000001</v>
       </c>
       <c r="E126" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="F126" t="n">
-        <v>624</v>
+        <v>2718</v>
       </c>
       <c r="G126" t="n">
-        <v>185.9</v>
+        <v>373.49</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I126" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="J126" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1314</v>
+      </c>
+      <c r="L126" t="n">
+        <v>106</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.925</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:19.415</t>
+          <t>2026-05-29 09:46:43.474</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1779509235231</v>
+        <v>1780022802315</v>
       </c>
       <c r="C127" t="n">
-        <v>87637</v>
+        <v>78094</v>
       </c>
       <c r="D127" t="n">
-        <v>103.93</v>
+        <v>-254.57</v>
       </c>
       <c r="E127" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="F127" t="n">
-        <v>685</v>
+        <v>2718</v>
       </c>
       <c r="G127" t="n">
-        <v>139.41</v>
+        <v>373.49</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I127" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J127" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1158</v>
+      </c>
+      <c r="L127" t="n">
+        <v>119</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.779</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:19.416</t>
+          <t>2026-05-29 09:46:43.700</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1779509235432</v>
+        <v>1780022802516</v>
       </c>
       <c r="C128" t="n">
-        <v>87246</v>
+        <v>75651</v>
       </c>
       <c r="D128" t="n">
-        <v>-292.27</v>
+        <v>-2684.84</v>
       </c>
       <c r="E128" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="F128" t="n">
-        <v>685</v>
+        <v>2718</v>
       </c>
       <c r="G128" t="n">
-        <v>139.41</v>
+        <v>373.49</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I128" t="n">
+        <v>49.58</v>
+      </c>
+      <c r="J128" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1184</v>
+      </c>
+      <c r="L128" t="n">
+        <v>110</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.552</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:20.107</t>
+          <t>2026-05-29 09:46:43.708</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1779509235634</v>
+        <v>1780022802715</v>
       </c>
       <c r="C129" t="n">
-        <v>87446</v>
+        <v>76201</v>
       </c>
       <c r="D129" t="n">
-        <v>-77.66</v>
+        <v>-2000.6</v>
       </c>
       <c r="E129" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="F129" t="n">
-        <v>685</v>
+        <v>2718</v>
       </c>
       <c r="G129" t="n">
-        <v>139.41</v>
+        <v>373.49</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I129" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J129" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K129" t="n">
+        <v>992</v>
+      </c>
+      <c r="L129" t="n">
+        <v>118</v>
+      </c>
+      <c r="M129" t="n">
+        <v>1.127</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:20.362</t>
+          <t>2026-05-29 09:46:43.755</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1779509235835</v>
+        <v>1780022802915</v>
       </c>
       <c r="C130" t="n">
-        <v>87671</v>
+        <v>74823</v>
       </c>
       <c r="D130" t="n">
-        <v>151.23</v>
+        <v>-3278.57</v>
       </c>
       <c r="E130" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="F130" t="n">
-        <v>685</v>
+        <v>2718</v>
       </c>
       <c r="G130" t="n">
-        <v>139.41</v>
+        <v>373.49</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I130" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J130" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K130" t="n">
+        <v>838</v>
+      </c>
+      <c r="L130" t="n">
+        <v>106</v>
+      </c>
+      <c r="M130" t="n">
+        <v>1.63</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:20.377</t>
+          <t>2026-05-29 09:46:44.459</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1779509236036</v>
+        <v>1780022803134</v>
       </c>
       <c r="C131" t="n">
-        <v>87578</v>
+        <v>76111</v>
       </c>
       <c r="D131" t="n">
-        <v>50.67</v>
+        <v>-1826.64</v>
       </c>
       <c r="E131" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="F131" t="n">
-        <v>644</v>
+        <v>2718</v>
       </c>
       <c r="G131" t="n">
-        <v>107.25</v>
+        <v>373.49</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I131" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J131" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1324</v>
+      </c>
+      <c r="L131" t="n">
+        <v>125</v>
+      </c>
+      <c r="M131" t="n">
+        <v>1.725</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:20.379</t>
+          <t>2026-05-29 09:46:44.524</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1779509236238</v>
+        <v>1780022803335</v>
       </c>
       <c r="C132" t="n">
-        <v>87475</v>
+        <v>75653</v>
       </c>
       <c r="D132" t="n">
-        <v>-54.87</v>
+        <v>-2193.31</v>
       </c>
       <c r="E132" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="F132" t="n">
-        <v>644</v>
+        <v>2718</v>
       </c>
       <c r="G132" t="n">
-        <v>107.25</v>
+        <v>373.49</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I132" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="J132" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1188</v>
+      </c>
+      <c r="L132" t="n">
+        <v>107</v>
+      </c>
+      <c r="M132" t="n">
+        <v>1.033</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:20.644</t>
+          <t>2026-05-29 09:46:44.525</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1779509236439</v>
+        <v>1780022803534</v>
       </c>
       <c r="C133" t="n">
-        <v>87600</v>
+        <v>74860</v>
       </c>
       <c r="D133" t="n">
-        <v>72.88</v>
+        <v>-2876.65</v>
       </c>
       <c r="E133" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="F133" t="n">
-        <v>644</v>
+        <v>2718</v>
       </c>
       <c r="G133" t="n">
-        <v>107.25</v>
+        <v>373.49</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I133" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J133" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K133" t="n">
+        <v>990</v>
+      </c>
+      <c r="L133" t="n">
+        <v>114</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.958</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:20.674</t>
+          <t>2026-05-29 09:46:44.526</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1779509236640</v>
+        <v>1780022803734</v>
       </c>
       <c r="C134" t="n">
-        <v>87814</v>
+        <v>74150</v>
       </c>
       <c r="D134" t="n">
-        <v>283.23</v>
+        <v>-3442.81</v>
       </c>
       <c r="E134" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="F134" t="n">
-        <v>705</v>
+        <v>2718</v>
       </c>
       <c r="G134" t="n">
-        <v>96.31</v>
+        <v>373.49</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I134" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J134" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K134" t="n">
+        <v>791</v>
+      </c>
+      <c r="L134" t="n">
+        <v>97</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.981</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:20.926</t>
+          <t>2026-05-29 09:46:45.003</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1779509236842</v>
+        <v>1780022803934</v>
       </c>
       <c r="C135" t="n">
-        <v>87403</v>
+        <v>73892</v>
       </c>
       <c r="D135" t="n">
-        <v>-141.93</v>
+        <v>-3528.67</v>
       </c>
       <c r="E135" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="F135" t="n">
-        <v>705</v>
+        <v>2718</v>
       </c>
       <c r="G135" t="n">
-        <v>96.31</v>
+        <v>373.49</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I135" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J135" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1067</v>
+      </c>
+      <c r="L135" t="n">
+        <v>108</v>
+      </c>
+      <c r="M135" t="n">
+        <v>1.151</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:21.188</t>
+          <t>2026-05-29 09:46:45.004</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1779509237043</v>
+        <v>1780022804134</v>
       </c>
       <c r="C136" t="n">
-        <v>87571</v>
+        <v>73997</v>
       </c>
       <c r="D136" t="n">
-        <v>33.17</v>
+        <v>-3247.24</v>
       </c>
       <c r="E136" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="F136" t="n">
-        <v>705</v>
+        <v>2718</v>
       </c>
       <c r="G136" t="n">
-        <v>96.31</v>
+        <v>373.49</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I136" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J136" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K136" t="n">
+        <v>869</v>
+      </c>
+      <c r="L136" t="n">
+        <v>108</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.769</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:21.645</t>
+          <t>2026-05-29 09:46:45.347</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1779509237244</v>
+        <v>1780022804334</v>
       </c>
       <c r="C137" t="n">
-        <v>87703</v>
+        <v>73984</v>
       </c>
       <c r="D137" t="n">
-        <v>163.51</v>
+        <v>-3097.88</v>
       </c>
       <c r="E137" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="F137" t="n">
-        <v>684</v>
+        <v>2718</v>
       </c>
       <c r="G137" t="n">
-        <v>96.31</v>
+        <v>373.49</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I137" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J137" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1012</v>
+      </c>
+      <c r="L137" t="n">
+        <v>114</v>
+      </c>
+      <c r="M137" t="n">
+        <v>1.225</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:21.920</t>
+          <t>2026-05-29 09:46:45.370</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1779509237446</v>
+        <v>1780022804534</v>
       </c>
       <c r="C138" t="n">
-        <v>87363</v>
+        <v>73993</v>
       </c>
       <c r="D138" t="n">
-        <v>-184.67</v>
+        <v>-2933.98</v>
       </c>
       <c r="E138" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="F138" t="n">
-        <v>684</v>
+        <v>2718</v>
       </c>
       <c r="G138" t="n">
-        <v>96.31</v>
+        <v>373.49</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I138" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J138" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K138" t="n">
+        <v>834</v>
+      </c>
+      <c r="L138" t="n">
+        <v>107</v>
+      </c>
+      <c r="M138" t="n">
+        <v>1.252</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:21.921</t>
+          <t>2026-05-29 09:46:46.100</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1779509237647</v>
+        <v>1780022804753</v>
       </c>
       <c r="C139" t="n">
-        <v>87485</v>
+        <v>73839</v>
       </c>
       <c r="D139" t="n">
-        <v>-53.43</v>
+        <v>-2941.28</v>
       </c>
       <c r="E139" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="F139" t="n">
-        <v>684</v>
+        <v>2718</v>
       </c>
       <c r="G139" t="n">
-        <v>96.31</v>
+        <v>373.49</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I139" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J139" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K139" t="n">
+        <v>1346</v>
+      </c>
+      <c r="L139" t="n">
+        <v>118</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.773</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:22.240</t>
+          <t>2026-05-29 09:46:46.116</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1779509237848</v>
+        <v>1780022804953</v>
       </c>
       <c r="C140" t="n">
-        <v>87610</v>
+        <v>73940</v>
       </c>
       <c r="D140" t="n">
-        <v>74.23999999999999</v>
+        <v>-2693.22</v>
       </c>
       <c r="E140" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="F140" t="n">
-        <v>684</v>
+        <v>2718</v>
       </c>
       <c r="G140" t="n">
-        <v>96.31</v>
+        <v>373.49</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I140" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J140" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K140" t="n">
+        <v>1162</v>
+      </c>
+      <c r="L140" t="n">
+        <v>108</v>
+      </c>
+      <c r="M140" t="n">
+        <v>1.114</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:22.534</t>
+          <t>2026-05-29 09:46:46.139</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1779509238050</v>
+        <v>1780022805153</v>
       </c>
       <c r="C141" t="n">
-        <v>87528</v>
+        <v>74362</v>
       </c>
       <c r="D141" t="n">
-        <v>-11.47</v>
+        <v>-2136.56</v>
       </c>
       <c r="E141" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F141" t="n">
-        <v>725</v>
+        <v>2718</v>
       </c>
       <c r="G141" t="n">
-        <v>46.86</v>
+        <v>373.49</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I141" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J141" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K141" t="n">
+        <v>985</v>
+      </c>
+      <c r="L141" t="n">
+        <v>107</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.953</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:22.535</t>
+          <t>2026-05-29 09:46:46.140</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1779509238251</v>
+        <v>1780022805353</v>
       </c>
       <c r="C142" t="n">
-        <v>87453</v>
+        <v>74478</v>
       </c>
       <c r="D142" t="n">
-        <v>-85.90000000000001</v>
+        <v>-1913.73</v>
       </c>
       <c r="E142" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F142" t="n">
-        <v>725</v>
+        <v>2718</v>
       </c>
       <c r="G142" t="n">
-        <v>46.86</v>
+        <v>373.49</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I142" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J142" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K142" t="n">
+        <v>786</v>
+      </c>
+      <c r="L142" t="n">
+        <v>109</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.969</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:23.086</t>
+          <t>2026-05-29 09:46:46.464</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1779509238452</v>
+        <v>1780022805553</v>
       </c>
       <c r="C143" t="n">
-        <v>87599</v>
+        <v>74366</v>
       </c>
       <c r="D143" t="n">
-        <v>64.40000000000001</v>
+        <v>-1930.04</v>
       </c>
       <c r="E143" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F143" t="n">
-        <v>725</v>
+        <v>2718</v>
       </c>
       <c r="G143" t="n">
-        <v>46.86</v>
+        <v>373.49</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I143" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J143" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K143" t="n">
+        <v>910</v>
+      </c>
+      <c r="L143" t="n">
+        <v>116</v>
+      </c>
+      <c r="M143" t="n">
+        <v>1.013</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:23.368</t>
+          <t>2026-05-29 09:46:46.465</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1779509238654</v>
+        <v>1780022805753</v>
       </c>
       <c r="C144" t="n">
-        <v>87763</v>
+        <v>74713</v>
       </c>
       <c r="D144" t="n">
-        <v>225.18</v>
+        <v>-1486.54</v>
       </c>
       <c r="E144" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="F144" t="n">
-        <v>584</v>
+        <v>2718</v>
       </c>
       <c r="G144" t="n">
-        <v>56.84</v>
+        <v>373.49</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I144" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J144" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K144" t="n">
+        <v>711</v>
+      </c>
+      <c r="L144" t="n">
+        <v>109</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0.966</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:23.369</t>
+          <t>2026-05-29 09:46:47.279</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>1779509238855</v>
+        <v>1780022805953</v>
       </c>
       <c r="C145" t="n">
-        <v>87393</v>
+        <v>75248</v>
       </c>
       <c r="D145" t="n">
-        <v>-156.08</v>
+        <v>-877.21</v>
       </c>
       <c r="E145" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="F145" t="n">
-        <v>584</v>
+        <v>2718</v>
       </c>
       <c r="G145" t="n">
-        <v>56.84</v>
+        <v>373.49</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I145" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J145" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K145" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L145" t="n">
+        <v>115</v>
+      </c>
+      <c r="M145" t="n">
+        <v>1.096</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:23.371</t>
+          <t>2026-05-29 09:46:47.280</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1779509239056</v>
+        <v>1780022806153</v>
       </c>
       <c r="C146" t="n">
-        <v>87571</v>
+        <v>75632</v>
       </c>
       <c r="D146" t="n">
-        <v>29.72</v>
+        <v>-449.35</v>
       </c>
       <c r="E146" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="F146" t="n">
-        <v>584</v>
+        <v>2718</v>
       </c>
       <c r="G146" t="n">
-        <v>56.84</v>
+        <v>373.49</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I146" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J146" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K146" t="n">
+        <v>1126</v>
+      </c>
+      <c r="L146" t="n">
+        <v>108</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0.974</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:23.667</t>
+          <t>2026-05-29 09:46:47.720</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1779509239258</v>
+        <v>1780022806372</v>
       </c>
       <c r="C147" t="n">
-        <v>87780</v>
+        <v>76131</v>
       </c>
       <c r="D147" t="n">
-        <v>237.23</v>
+        <v>72.11</v>
       </c>
       <c r="E147" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="F147" t="n">
-        <v>665</v>
+        <v>2718</v>
       </c>
       <c r="G147" t="n">
-        <v>55.72</v>
+        <v>373.49</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I147" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J147" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K147" t="n">
+        <v>1346</v>
+      </c>
+      <c r="L147" t="n">
+        <v>114</v>
+      </c>
+      <c r="M147" t="n">
+        <v>1.43</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:23.678</t>
+          <t>2026-05-29 09:46:47.736</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>1779509239459</v>
+        <v>1780022806572</v>
       </c>
       <c r="C148" t="n">
-        <v>87469</v>
+        <v>75961</v>
       </c>
       <c r="D148" t="n">
-        <v>-85.63</v>
+        <v>-101.49</v>
       </c>
       <c r="E148" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="F148" t="n">
-        <v>665</v>
+        <v>2718</v>
       </c>
       <c r="G148" t="n">
-        <v>55.72</v>
+        <v>373.49</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I148" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J148" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K148" t="n">
+        <v>1163</v>
+      </c>
+      <c r="L148" t="n">
+        <v>111</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0.959</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:23.724</t>
+          <t>2026-05-29 09:46:47.759</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1779509239660</v>
+        <v>1780022806772</v>
       </c>
       <c r="C149" t="n">
-        <v>87611</v>
+        <v>75695</v>
       </c>
       <c r="D149" t="n">
-        <v>60.65</v>
+        <v>-362.42</v>
       </c>
       <c r="E149" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="F149" t="n">
-        <v>665</v>
+        <v>2718</v>
       </c>
       <c r="G149" t="n">
-        <v>55.72</v>
+        <v>373.49</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I149" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J149" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K149" t="n">
+        <v>986</v>
+      </c>
+      <c r="L149" t="n">
+        <v>112</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0.845</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:24.011</t>
+          <t>2026-05-29 09:46:47.761</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>1779509239862</v>
+        <v>1780022806972</v>
       </c>
       <c r="C150" t="n">
-        <v>87796</v>
+        <v>75771</v>
       </c>
       <c r="D150" t="n">
-        <v>242.62</v>
+        <v>-268.3</v>
       </c>
       <c r="E150" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="F150" t="n">
-        <v>665</v>
+        <v>2718</v>
       </c>
       <c r="G150" t="n">
-        <v>55.72</v>
+        <v>373.49</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I150" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J150" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K150" t="n">
+        <v>788</v>
+      </c>
+      <c r="L150" t="n">
+        <v>112</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0.949</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-05-23 11:07:24.317</t>
+          <t>2026-05-29 09:46:48.556</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1779509240063</v>
+        <v>1780022807172</v>
       </c>
       <c r="C151" t="n">
-        <v>87937</v>
+        <v>76015</v>
       </c>
       <c r="D151" t="n">
-        <v>371.49</v>
+        <v>-10.88</v>
       </c>
       <c r="E151" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="F151" t="n">
-        <v>664</v>
+        <v>2718</v>
       </c>
       <c r="G151" t="n">
-        <v>51.36</v>
+        <v>373.49</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
       </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:07:25.563</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>1779509240265</v>
-      </c>
-      <c r="C152" t="n">
-        <v>87568</v>
-      </c>
-      <c r="D152" t="n">
-        <v>-16.08</v>
-      </c>
-      <c r="E152" t="n">
-        <v>91</v>
-      </c>
-      <c r="F152" t="n">
-        <v>664</v>
-      </c>
-      <c r="G152" t="n">
-        <v>51.36</v>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
+      <c r="I151" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J151" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K151" t="n">
+        <v>1382</v>
+      </c>
+      <c r="L151" t="n">
+        <v>108</v>
+      </c>
+      <c r="M151" t="n">
+        <v>1.244</v>
       </c>
     </row>
   </sheetData>
